--- a/мат стат/эспер данные/Обработка_эксперементальных_данных_Элизбарян Э,В,.xlsx
+++ b/мат стат/эспер данные/Обработка_эксперементальных_данных_Элизбарян Э,В,.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emin\4_semestr\мат стат\эспер данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFAA039-C994-4572-B7E9-5F62750BC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5543A664-F9DE-440C-B1DC-CE09DF586405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="2670" windowWidth="14595" windowHeight="8895" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задача1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
   <si>
     <t>n</t>
   </si>
@@ -112,6 +112,96 @@
   </si>
   <si>
     <t>Точноть</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>b ср</t>
+  </si>
+  <si>
+    <t>b ср квад откл</t>
+  </si>
+  <si>
+    <t>сл погреш</t>
+  </si>
+  <si>
+    <t>Довер веро</t>
+  </si>
+  <si>
+    <t>Погрешность</t>
+  </si>
+  <si>
+    <t>Общая погрешность</t>
+  </si>
+  <si>
+    <t>Доверительный интервал</t>
+  </si>
+  <si>
+    <t>12.8-0.25</t>
+  </si>
+  <si>
+    <t>12.8+0.25</t>
+  </si>
+  <si>
+    <t>a ср</t>
+  </si>
+  <si>
+    <t>ско</t>
+  </si>
+  <si>
+    <t>погрешность прибора</t>
+  </si>
+  <si>
+    <t>погрешность штангенциркуля</t>
+  </si>
+  <si>
+    <t>Дов интервал</t>
+  </si>
+  <si>
+    <t>12.7+-0.05</t>
+  </si>
+  <si>
+    <t>h ср</t>
+  </si>
+  <si>
+    <t>ско среднего</t>
+  </si>
+  <si>
+    <t>случ погрешн</t>
+  </si>
+  <si>
+    <t>общ погрешность</t>
+  </si>
+  <si>
+    <t>14.8+-0.3</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>уровень значимости</t>
+  </si>
+  <si>
+    <t>ср</t>
+  </si>
+  <si>
+    <t>выбор станд откло</t>
+  </si>
+  <si>
+    <t>станд ошибка среднег</t>
+  </si>
+  <si>
+    <t>абсолютн погрешность</t>
+  </si>
+  <si>
+    <t>15.4083+-0.026065</t>
   </si>
 </sst>
 </file>
@@ -163,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -740,30 +830,31 @@
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -772,99 +863,111 @@
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>47.12</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <f>(A2-C10)^2</f>
         <v>1.0000000000010231E-4</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <f>SUM(B2:B4)</f>
         <v>1.4000000000001533E-3</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <f>C2/2</f>
         <v>7.0000000000007665E-4</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <f>SQRT(D2)</f>
         <v>2.6457513110647354E-2</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <f>E2/SQRT(3)</f>
         <v>1.5275252316520304E-2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>4.3029999999999999</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>47.08</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <f>(A3-C10)^2</f>
         <v>8.9999999999964186E-4</v>
       </c>
-      <c r="H3">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2">
         <v>47.044260000000001</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>47.175739999999998</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>47.13</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <f>(A4-C10)^2</f>
         <v>4.0000000000040925E-4</v>
       </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>3</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>0.95</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <f>AVERAGE(A2:A4)</f>
         <v>47.109999999999992</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>47.11</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F12">
+      <c r="F12" s="2">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -878,18 +981,385 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1002DF87-E478-4FB2-9908-634279CEFB1D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>15.42</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
+        <v>15.408300000000001</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2.4832E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1.0137999999999999E-2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2.5710000000000002</v>
+      </c>
+      <c r="H2" s="2">
+        <f>G2*F2</f>
+        <v>2.6064798E-2</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>15.45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>15.41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>15.39</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BB4507-238B-4561-AD7D-C2A81A950461}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="7" max="7" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="G2" s="2">
+        <f>C2-F2</f>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <f>H2/SQRT(A4)</f>
+        <v>5.7735026918962581E-2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="K2" s="2">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="M2" s="2">
+        <f>L2*H2</f>
+        <v>0.43</v>
+      </c>
+      <c r="N2" s="2">
+        <f>L2*I2</f>
+        <v>0.2482606157515391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="D3" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2">
+        <f>C3-F2</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="C4" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="D4" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
+        <f>C4-F2</f>
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="C5" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F10" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="2">
+        <f>I10/2</f>
+        <v>0.05</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F14" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="I14" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="2">
+        <f>B5*C5*D5</f>
+        <v>2405.8880000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="L5:M5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>